--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/whitespace_pref.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/whitespace_pref.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C2" t="n">
-        <v>73.5</v>
+        <v>73.66</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C3" t="n">
-        <v>13.5</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         <v>26</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>11.61</v>
       </c>
     </row>
   </sheetData>
